--- a/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mz_2021_2025.xlsx
+++ b/data/cleaned/cleaned_swq_physical_parameter_manual_cpcb_mz_2021_2025.xlsx
@@ -626,7 +626,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T2" t="n">
@@ -727,7 +727,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T3" t="n">
@@ -828,7 +828,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T4" t="inlineStr"/>
@@ -921,7 +921,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T5" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T6" t="inlineStr"/>
@@ -1107,7 +1107,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T7" t="n">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T8" t="n">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T9" t="n">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T10" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T11" t="inlineStr"/>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T12" t="inlineStr"/>
@@ -1697,7 +1697,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T13" t="inlineStr"/>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T14" t="n">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T15" t="n">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T16" t="n">
@@ -2093,7 +2093,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T17" t="inlineStr"/>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T18" t="inlineStr"/>
@@ -2279,7 +2279,7 @@
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T19" t="inlineStr"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T20" t="inlineStr"/>
@@ -2465,7 +2465,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>01-02-2021 08:30</t>
+          <t>2021-01-02 08:30:00</t>
         </is>
       </c>
       <c r="T21" t="inlineStr"/>
@@ -2558,7 +2558,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T22" t="inlineStr"/>
@@ -2651,7 +2651,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T23" t="inlineStr"/>
@@ -2744,7 +2744,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T24" t="inlineStr"/>
@@ -2837,7 +2837,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T25" t="inlineStr"/>
@@ -2930,7 +2930,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T26" t="n">
@@ -3031,7 +3031,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T27" t="n">
@@ -3132,7 +3132,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T28" t="n">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T29" t="n">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>06-04-2021 08:30</t>
+          <t>2021-06-04 08:30:00</t>
         </is>
       </c>
       <c r="T30" t="n">
@@ -3435,7 +3435,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T31" t="n">
@@ -3536,7 +3536,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T32" t="inlineStr"/>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T33" t="inlineStr"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T34" t="inlineStr"/>
@@ -3815,7 +3815,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T35" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T36" t="n">
@@ -4017,7 +4017,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T37" t="n">
@@ -4118,7 +4118,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T38" t="n">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T39" t="n">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T40" t="n">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T41" t="n">
@@ -4522,7 +4522,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T42" t="n">
@@ -4623,7 +4623,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T43" t="inlineStr"/>
@@ -4716,7 +4716,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T44" t="inlineStr"/>
@@ -4809,7 +4809,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T45" t="inlineStr"/>
@@ -4902,7 +4902,7 @@
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T46" t="n">
@@ -4997,7 +4997,7 @@
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T47" t="n">
@@ -5092,7 +5092,7 @@
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T48" t="n">
@@ -5187,7 +5187,7 @@
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T49" t="n">
@@ -5282,7 +5282,7 @@
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>07-05-2021 08:30</t>
+          <t>2021-07-05 08:30:00</t>
         </is>
       </c>
       <c r="T50" t="n">
@@ -5377,7 +5377,7 @@
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>11-06-2021 08:30</t>
+          <t>2021-11-06 08:30:00</t>
         </is>
       </c>
       <c r="T51" t="n">
@@ -5472,7 +5472,7 @@
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>09-07-2021 08:30</t>
+          <t>2021-09-07 08:30:00</t>
         </is>
       </c>
       <c r="T52" t="n">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>13-08-2021 08:30</t>
+          <t>2021-08-13 08:30:00</t>
         </is>
       </c>
       <c r="T53" t="n">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>09-09-2021 08:30</t>
+          <t>2021-09-09 08:30:00</t>
         </is>
       </c>
       <c r="T54" t="n">
@@ -5757,7 +5757,7 @@
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T55" t="n">
@@ -5852,7 +5852,7 @@
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>10-11-2021 08:30</t>
+          <t>2021-10-11 08:30:00</t>
         </is>
       </c>
       <c r="T56" t="n">
@@ -5947,7 +5947,7 @@
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>03-12-2021 08:30</t>
+          <t>2021-03-12 08:30:00</t>
         </is>
       </c>
       <c r="T57" t="n">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T58" t="inlineStr"/>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>05-02-2021 08:30</t>
+          <t>2021-05-02 08:30:00</t>
         </is>
       </c>
       <c r="T59" t="inlineStr"/>
@@ -6228,7 +6228,7 @@
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>12-03-2021 08:30</t>
+          <t>2021-12-03 08:30:00</t>
         </is>
       </c>
       <c r="T60" t="inlineStr"/>
@@ -6321,7 +6321,7 @@
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T61" t="n">
@@ -6422,7 +6422,7 @@
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T62" t="n">
@@ -6521,7 +6521,7 @@
       </c>
       <c r="S63" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T63" t="n">
@@ -6622,7 +6622,7 @@
       </c>
       <c r="S64" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T64" t="inlineStr"/>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="S65" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T65" t="inlineStr"/>
@@ -6808,7 +6808,7 @@
       </c>
       <c r="S66" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T66" t="inlineStr"/>
@@ -6901,7 +6901,7 @@
       </c>
       <c r="S67" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T67" t="n">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="S68" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T68" t="n">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>18-10-2021 08:30</t>
+          <t>2021-10-18 08:30:00</t>
         </is>
       </c>
       <c r="T69" t="n">
@@ -7204,7 +7204,7 @@
       </c>
       <c r="S70" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T70" t="inlineStr"/>
@@ -7297,7 +7297,7 @@
       </c>
       <c r="S71" t="inlineStr">
         <is>
-          <t>22-02-2021 08:30</t>
+          <t>2021-02-22 08:30:00</t>
         </is>
       </c>
       <c r="T71" t="inlineStr"/>
@@ -7390,7 +7390,7 @@
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T72" t="inlineStr"/>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="S73" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T73" t="n">
@@ -7584,7 +7584,7 @@
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>10-04-2021 08:30</t>
+          <t>2021-10-04 08:30:00</t>
         </is>
       </c>
       <c r="T74" t="n">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="S75" t="inlineStr">
         <is>
-          <t>15-10-2021 08:30</t>
+          <t>2021-10-15 08:30:00</t>
         </is>
       </c>
       <c r="T75" t="n">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T76" t="n">
@@ -7887,7 +7887,7 @@
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>12-04-2021 08:30</t>
+          <t>2021-12-04 08:30:00</t>
         </is>
       </c>
       <c r="T77" t="n">
@@ -7988,7 +7988,7 @@
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T78" t="n">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>15-11-2021 08:30</t>
+          <t>2021-11-15 08:30:00</t>
         </is>
       </c>
       <c r="T79" t="n">
@@ -8190,7 +8190,7 @@
       </c>
       <c r="S80" t="inlineStr">
         <is>
-          <t>08-01-2021 08:30</t>
+          <t>2021-08-01 08:30:00</t>
         </is>
       </c>
       <c r="T80" t="inlineStr"/>
@@ -8283,7 +8283,7 @@
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T81" t="inlineStr"/>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="S82" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T82" t="inlineStr"/>
@@ -8469,7 +8469,7 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T83" t="n">
@@ -8564,7 +8564,7 @@
       </c>
       <c r="S84" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T84" t="n">
@@ -8659,7 +8659,7 @@
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>23-03-2021 08:30</t>
+          <t>2021-03-23 08:30:00</t>
         </is>
       </c>
       <c r="T85" t="n">
@@ -8754,7 +8754,7 @@
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T86" t="n">
@@ -8849,7 +8849,7 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>31-05-2021 08:30</t>
+          <t>2021-05-31 08:30:00</t>
         </is>
       </c>
       <c r="T87" t="n">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>03-06-2021 08:30</t>
+          <t>2021-03-06 08:30:00</t>
         </is>
       </c>
       <c r="T88" t="n">
@@ -9039,7 +9039,7 @@
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>15-07-2021 08:30</t>
+          <t>2021-07-15 08:30:00</t>
         </is>
       </c>
       <c r="T89" t="n">
@@ -9134,7 +9134,7 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>05-08-2021 08:30</t>
+          <t>2021-05-08 08:30:00</t>
         </is>
       </c>
       <c r="T90" t="n">
@@ -9229,7 +9229,7 @@
       </c>
       <c r="S91" t="inlineStr">
         <is>
-          <t>27-09-2021 08:30</t>
+          <t>2021-09-27 08:30:00</t>
         </is>
       </c>
       <c r="T91" t="n">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>22-10-2021 08:30</t>
+          <t>2021-10-22 08:30:00</t>
         </is>
       </c>
       <c r="T92" t="n">
@@ -9419,7 +9419,7 @@
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>18-11-2021 08:30</t>
+          <t>2021-11-18 08:30:00</t>
         </is>
       </c>
       <c r="T93" t="n">
@@ -9514,7 +9514,7 @@
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>08-12-2021 08:30</t>
+          <t>2021-08-12 08:30:00</t>
         </is>
       </c>
       <c r="T94" t="n">
@@ -9609,7 +9609,7 @@
       </c>
       <c r="S95" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T95" t="inlineStr"/>
@@ -9702,7 +9702,7 @@
       </c>
       <c r="S96" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T96" t="inlineStr"/>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T97" t="inlineStr"/>
@@ -9888,7 +9888,7 @@
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T98" t="inlineStr"/>
@@ -9981,7 +9981,7 @@
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T99" t="inlineStr"/>
@@ -10074,7 +10074,7 @@
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T100" t="inlineStr"/>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T101" t="n">
@@ -10262,7 +10262,7 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>14-02-2021 08:30</t>
+          <t>2021-02-14 08:30:00</t>
         </is>
       </c>
       <c r="T102" t="n">
@@ -10357,7 +10357,7 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T103" t="n">
@@ -10452,7 +10452,7 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>11-04-2021 08:30</t>
+          <t>2021-11-04 08:30:00</t>
         </is>
       </c>
       <c r="T104" t="n">
@@ -10547,7 +10547,7 @@
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>31-05-2021 08:30</t>
+          <t>2021-05-31 08:30:00</t>
         </is>
       </c>
       <c r="T105" t="n">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>30-06-2021 08:30</t>
+          <t>2021-06-30 08:30:00</t>
         </is>
       </c>
       <c r="T106" t="n">
@@ -10737,7 +10737,7 @@
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>30-07-2021 08:30</t>
+          <t>2021-07-30 08:30:00</t>
         </is>
       </c>
       <c r="T107" t="n">
@@ -10832,7 +10832,7 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>10-08-2021 08:30</t>
+          <t>2021-10-08 08:30:00</t>
         </is>
       </c>
       <c r="T108" t="n">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>19-09-2021 08:30</t>
+          <t>2021-09-19 08:30:00</t>
         </is>
       </c>
       <c r="T109" t="n">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>19-10-2021 08:30</t>
+          <t>2021-10-19 08:30:00</t>
         </is>
       </c>
       <c r="T110" t="n">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>06-11-2021 08:30</t>
+          <t>2021-06-11 08:30:00</t>
         </is>
       </c>
       <c r="T111" t="n">
@@ -11212,7 +11212,7 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>19-12-2021 08:30</t>
+          <t>2021-12-19 08:30:00</t>
         </is>
       </c>
       <c r="T112" t="n">
@@ -11307,7 +11307,7 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T113" t="n">
@@ -11408,7 +11408,7 @@
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T114" t="n">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T115" t="n">
@@ -11610,7 +11610,7 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T116" t="n">
@@ -11711,7 +11711,7 @@
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T117" t="n">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>25-01-2021 08:30</t>
+          <t>2021-01-25 08:30:00</t>
         </is>
       </c>
       <c r="T118" t="n">
@@ -11913,7 +11913,7 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>05-04-2021 08:30</t>
+          <t>2021-05-04 08:30:00</t>
         </is>
       </c>
       <c r="T119" t="n">
@@ -12014,7 +12014,7 @@
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>14-10-2021 08:30</t>
+          <t>2021-10-14 08:30:00</t>
         </is>
       </c>
       <c r="T120" t="n">
@@ -12115,7 +12115,7 @@
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T121" t="inlineStr"/>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="S122" t="inlineStr">
         <is>
-          <t>25-02-2021 08:30</t>
+          <t>2021-02-25 08:30:00</t>
         </is>
       </c>
       <c r="T122" t="inlineStr"/>
@@ -12301,7 +12301,7 @@
       </c>
       <c r="S123" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T123" t="inlineStr"/>
@@ -12394,7 +12394,7 @@
       </c>
       <c r="S124" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T124" t="inlineStr"/>
@@ -12487,7 +12487,7 @@
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>12-02-2021 08:30</t>
+          <t>2021-12-02 08:30:00</t>
         </is>
       </c>
       <c r="T125" t="inlineStr"/>
@@ -12580,7 +12580,7 @@
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>16-03-2021 08:30</t>
+          <t>2021-03-16 08:30:00</t>
         </is>
       </c>
       <c r="T126" t="inlineStr"/>
@@ -12673,7 +12673,7 @@
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T127" t="n">
@@ -12774,7 +12774,7 @@
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>14-04-2021 08:30</t>
+          <t>2021-04-14 08:30:00</t>
         </is>
       </c>
       <c r="T128" t="n">
@@ -12875,7 +12875,7 @@
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>16-10-2021 08:30</t>
+          <t>2021-10-16 08:30:00</t>
         </is>
       </c>
       <c r="T129" t="n">
@@ -12976,7 +12976,7 @@
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>26-04-2021 08:30</t>
+          <t>2021-04-26 08:30:00</t>
         </is>
       </c>
       <c r="T130" t="n">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T131" t="n">
@@ -13178,7 +13178,7 @@
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T132" t="inlineStr"/>
@@ -13271,7 +13271,7 @@
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>21-02-2021 08:30</t>
+          <t>2021-02-21 08:30:00</t>
         </is>
       </c>
       <c r="T133" t="inlineStr"/>
@@ -13364,7 +13364,7 @@
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T134" t="inlineStr"/>
@@ -13457,7 +13457,7 @@
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T135" t="inlineStr"/>
@@ -13550,7 +13550,7 @@
       </c>
       <c r="S136" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T136" t="inlineStr"/>
@@ -13643,7 +13643,7 @@
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T137" t="inlineStr"/>
@@ -13736,7 +13736,7 @@
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T138" t="inlineStr"/>
@@ -13829,7 +13829,7 @@
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T139" t="inlineStr"/>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T140" t="inlineStr"/>
@@ -14015,7 +14015,7 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>20-04-2021 08:30</t>
+          <t>2021-04-20 08:30:00</t>
         </is>
       </c>
       <c r="T141" t="n">
@@ -14116,7 +14116,7 @@
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>07-10-2021 08:30</t>
+          <t>2021-07-10 08:30:00</t>
         </is>
       </c>
       <c r="T142" t="n">
@@ -14217,7 +14217,7 @@
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T143" t="n">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T144" t="n">
@@ -14407,7 +14407,7 @@
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T145" t="n">
@@ -14502,7 +14502,7 @@
       </c>
       <c r="S146" t="inlineStr">
         <is>
-          <t>17-04-2021 08:30</t>
+          <t>2021-04-17 08:30:00</t>
         </is>
       </c>
       <c r="T146" t="n">
@@ -14597,7 +14597,7 @@
       </c>
       <c r="S147" t="inlineStr">
         <is>
-          <t>14-05-2021 08:30</t>
+          <t>2021-05-14 08:30:00</t>
         </is>
       </c>
       <c r="T147" t="n">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="S148" t="inlineStr">
         <is>
-          <t>18-06-2021 08:30</t>
+          <t>2021-06-18 08:30:00</t>
         </is>
       </c>
       <c r="T148" t="n">
@@ -14787,7 +14787,7 @@
       </c>
       <c r="S149" t="inlineStr">
         <is>
-          <t>19-07-2021 08:30</t>
+          <t>2021-07-19 08:30:00</t>
         </is>
       </c>
       <c r="T149" t="n">
@@ -14882,7 +14882,7 @@
       </c>
       <c r="S150" t="inlineStr">
         <is>
-          <t>07-08-2021 08:30</t>
+          <t>2021-07-08 08:30:00</t>
         </is>
       </c>
       <c r="T150" t="n">
@@ -14977,7 +14977,7 @@
       </c>
       <c r="S151" t="inlineStr">
         <is>
-          <t>17-09-2021 08:30</t>
+          <t>2021-09-17 08:30:00</t>
         </is>
       </c>
       <c r="T151" t="n">
@@ -15072,7 +15072,7 @@
       </c>
       <c r="S152" t="inlineStr">
         <is>
-          <t>25-10-2021 08:30</t>
+          <t>2021-10-25 08:30:00</t>
         </is>
       </c>
       <c r="T152" t="n">
@@ -15167,7 +15167,7 @@
       </c>
       <c r="S153" t="inlineStr">
         <is>
-          <t>20-11-2021 08:30</t>
+          <t>2021-11-20 08:30:00</t>
         </is>
       </c>
       <c r="T153" t="n">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="S154" t="inlineStr">
         <is>
-          <t>11-12-2021 08:30</t>
+          <t>2021-11-12 08:30:00</t>
         </is>
       </c>
       <c r="T154" t="n">
@@ -15357,7 +15357,7 @@
       </c>
       <c r="S155" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T155" t="inlineStr"/>
@@ -15450,7 +15450,7 @@
       </c>
       <c r="S156" t="inlineStr">
         <is>
-          <t>14-02-2021 08:30</t>
+          <t>2021-02-14 08:30:00</t>
         </is>
       </c>
       <c r="T156" t="inlineStr"/>
@@ -15543,7 +15543,7 @@
       </c>
       <c r="S157" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T157" t="inlineStr"/>
@@ -15636,7 +15636,7 @@
       </c>
       <c r="S158" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T158" t="inlineStr"/>
@@ -15729,7 +15729,7 @@
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T159" t="inlineStr"/>
@@ -15822,7 +15822,7 @@
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T160" t="inlineStr"/>
@@ -15915,7 +15915,7 @@
       </c>
       <c r="S161" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T161" t="inlineStr"/>
@@ -16008,7 +16008,7 @@
       </c>
       <c r="S162" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T162" t="inlineStr"/>
@@ -16101,7 +16101,7 @@
       </c>
       <c r="S163" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T163" t="inlineStr"/>
@@ -16194,7 +16194,7 @@
       </c>
       <c r="S164" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T164" t="inlineStr"/>
@@ -16287,7 +16287,7 @@
       </c>
       <c r="S165" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T165" t="inlineStr"/>
@@ -16380,7 +16380,7 @@
       </c>
       <c r="S166" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T166" t="inlineStr"/>
@@ -16473,7 +16473,7 @@
       </c>
       <c r="S167" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T167" t="inlineStr"/>
@@ -16566,7 +16566,7 @@
       </c>
       <c r="S168" t="inlineStr">
         <is>
-          <t>14-02-2021 08:30</t>
+          <t>2021-02-14 08:30:00</t>
         </is>
       </c>
       <c r="T168" t="inlineStr"/>
@@ -16659,7 +16659,7 @@
       </c>
       <c r="S169" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T169" t="inlineStr"/>
@@ -16752,7 +16752,7 @@
       </c>
       <c r="S170" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T170" t="inlineStr"/>
@@ -16845,7 +16845,7 @@
       </c>
       <c r="S171" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T171" t="inlineStr"/>
@@ -16938,7 +16938,7 @@
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T172" t="inlineStr"/>
@@ -17031,7 +17031,7 @@
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>18-01-2021 08:30</t>
+          <t>2021-01-18 08:30:00</t>
         </is>
       </c>
       <c r="T173" t="inlineStr"/>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T174" t="inlineStr"/>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T175" t="inlineStr"/>
@@ -17310,7 +17310,7 @@
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>10-01-2021 08:30</t>
+          <t>2021-10-01 08:30:00</t>
         </is>
       </c>
       <c r="T176" t="inlineStr"/>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>14-02-2021 08:30</t>
+          <t>2021-02-14 08:30:00</t>
         </is>
       </c>
       <c r="T177" t="inlineStr"/>
@@ -17496,7 +17496,7 @@
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T178" t="inlineStr"/>
@@ -17589,7 +17589,7 @@
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>14-01-2021 08:30</t>
+          <t>2021-01-14 08:30:00</t>
         </is>
       </c>
       <c r="T179" t="inlineStr"/>
@@ -17682,7 +17682,7 @@
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T180" t="inlineStr"/>
@@ -17775,7 +17775,7 @@
       </c>
       <c r="S181" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T181" t="inlineStr"/>
@@ -17868,7 +17868,7 @@
       </c>
       <c r="S182" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T182" t="inlineStr"/>
@@ -17961,7 +17961,7 @@
       </c>
       <c r="S183" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T183" t="inlineStr"/>
@@ -18054,7 +18054,7 @@
       </c>
       <c r="S184" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T184" t="inlineStr"/>
@@ -18147,7 +18147,7 @@
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>06-01-2021 08:30</t>
+          <t>2021-06-01 08:30:00</t>
         </is>
       </c>
       <c r="T185" t="inlineStr"/>
@@ -18240,7 +18240,7 @@
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>03-02-2021 08:30</t>
+          <t>2021-03-02 08:30:00</t>
         </is>
       </c>
       <c r="T186" t="inlineStr"/>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T187" t="inlineStr"/>
@@ -18426,7 +18426,7 @@
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>13-10-2021 08:30</t>
+          <t>2021-10-13 08:30:00</t>
         </is>
       </c>
       <c r="T188" t="n">
@@ -18527,7 +18527,7 @@
       </c>
       <c r="S189" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T189" t="inlineStr"/>
@@ -18620,7 +18620,7 @@
       </c>
       <c r="S190" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T190" t="inlineStr"/>
@@ -18713,7 +18713,7 @@
       </c>
       <c r="S191" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T191" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="S192" t="inlineStr">
         <is>
-          <t>19-01-2021 08:30</t>
+          <t>2021-01-19 08:30:00</t>
         </is>
       </c>
       <c r="T192" t="inlineStr"/>
@@ -18899,7 +18899,7 @@
       </c>
       <c r="S193" t="inlineStr">
         <is>
-          <t>09-02-2021 08:30</t>
+          <t>2021-09-02 08:30:00</t>
         </is>
       </c>
       <c r="T193" t="inlineStr"/>
@@ -18992,7 +18992,7 @@
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>09-03-2021 08:30</t>
+          <t>2021-09-03 08:30:00</t>
         </is>
       </c>
       <c r="T194" t="inlineStr"/>
@@ -19085,7 +19085,7 @@
       </c>
       <c r="S195" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T195" t="inlineStr"/>
@@ -19178,7 +19178,7 @@
       </c>
       <c r="S196" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T196" t="inlineStr"/>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>15-03-2021 08:30</t>
+          <t>2021-03-15 08:30:00</t>
         </is>
       </c>
       <c r="T197" t="inlineStr"/>
@@ -19364,7 +19364,7 @@
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T198" t="inlineStr"/>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="S199" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T199" t="inlineStr"/>
@@ -19550,7 +19550,7 @@
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T200" t="inlineStr"/>
@@ -19643,7 +19643,7 @@
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T201" t="inlineStr"/>
@@ -19736,7 +19736,7 @@
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>15-02-2021 08:30</t>
+          <t>2021-02-15 08:30:00</t>
         </is>
       </c>
       <c r="T202" t="inlineStr"/>
@@ -19829,7 +19829,7 @@
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T203" t="inlineStr"/>
@@ -19922,7 +19922,7 @@
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>15-01-2021 08:30</t>
+          <t>2021-01-15 08:30:00</t>
         </is>
       </c>
       <c r="T204" t="inlineStr"/>
@@ -20015,7 +20015,7 @@
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T205" t="inlineStr"/>
@@ -20108,7 +20108,7 @@
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T206" t="inlineStr"/>
@@ -20201,7 +20201,7 @@
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>22-01-2021 08:30</t>
+          <t>2021-01-22 08:30:00</t>
         </is>
       </c>
       <c r="T207" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="S208" t="inlineStr">
         <is>
-          <t>20-02-2021 08:30</t>
+          <t>2021-02-20 08:30:00</t>
         </is>
       </c>
       <c r="T208" t="inlineStr"/>
@@ -20387,7 +20387,7 @@
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T209" t="inlineStr"/>
@@ -20480,7 +20480,7 @@
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T210" t="inlineStr"/>
@@ -20573,7 +20573,7 @@
       </c>
       <c r="S211" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T211" t="inlineStr"/>
@@ -20666,7 +20666,7 @@
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T212" t="inlineStr"/>
@@ -20759,7 +20759,7 @@
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T213" t="inlineStr"/>
@@ -20852,7 +20852,7 @@
       </c>
       <c r="S214" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T214" t="inlineStr"/>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="S215" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T215" t="inlineStr"/>
@@ -21038,7 +21038,7 @@
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T216" t="inlineStr"/>
@@ -21131,7 +21131,7 @@
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T217" t="inlineStr"/>
@@ -21224,7 +21224,7 @@
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T218" t="inlineStr"/>
@@ -21317,7 +21317,7 @@
       </c>
       <c r="S219" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T219" t="inlineStr"/>
@@ -21410,7 +21410,7 @@
       </c>
       <c r="S220" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T220" t="inlineStr"/>
@@ -21503,7 +21503,7 @@
       </c>
       <c r="S221" t="inlineStr">
         <is>
-          <t>18-03-2021 08:30</t>
+          <t>2021-03-18 08:30:00</t>
         </is>
       </c>
       <c r="T221" t="inlineStr"/>
@@ -21596,7 +21596,7 @@
       </c>
       <c r="S222" t="inlineStr">
         <is>
-          <t>05-01-2021 08:30</t>
+          <t>2021-05-01 08:30:00</t>
         </is>
       </c>
       <c r="T222" t="inlineStr"/>
@@ -21689,7 +21689,7 @@
       </c>
       <c r="S223" t="inlineStr">
         <is>
-          <t>02-02-2021 08:30</t>
+          <t>2021-02-02 08:30:00</t>
         </is>
       </c>
       <c r="T223" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="S224" t="inlineStr">
         <is>
-          <t>02-03-2021 08:30</t>
+          <t>2021-02-03 08:30:00</t>
         </is>
       </c>
       <c r="T224" t="inlineStr"/>
@@ -21875,7 +21875,7 @@
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T225" t="inlineStr"/>
@@ -21968,7 +21968,7 @@
       </c>
       <c r="S226" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T226" t="inlineStr"/>
@@ -22061,7 +22061,7 @@
       </c>
       <c r="S227" t="inlineStr">
         <is>
-          <t>17-03-2021 08:30</t>
+          <t>2021-03-17 08:30:00</t>
         </is>
       </c>
       <c r="T227" t="inlineStr"/>
@@ -22154,7 +22154,7 @@
       </c>
       <c r="S228" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T228" t="n">
@@ -22255,7 +22255,7 @@
       </c>
       <c r="S229" t="inlineStr">
         <is>
-          <t>09-04-2021 08:30</t>
+          <t>2021-09-04 08:30:00</t>
         </is>
       </c>
       <c r="T229" t="n">
@@ -22356,7 +22356,7 @@
       </c>
       <c r="S230" t="inlineStr">
         <is>
-          <t>05-10-2021 08:30</t>
+          <t>2021-05-10 08:30:00</t>
         </is>
       </c>
       <c r="T230" t="n">
@@ -22457,7 +22457,7 @@
       </c>
       <c r="S231" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T231" t="n">
@@ -22558,7 +22558,7 @@
       </c>
       <c r="S232" t="inlineStr">
         <is>
-          <t>19-04-2021 08:30</t>
+          <t>2021-04-19 08:30:00</t>
         </is>
       </c>
       <c r="T232" t="n">
@@ -22659,7 +22659,7 @@
       </c>
       <c r="S233" t="inlineStr">
         <is>
-          <t>27-10-2021 08:30</t>
+          <t>2021-10-27 08:30:00</t>
         </is>
       </c>
       <c r="T233" t="n">
@@ -22760,7 +22760,7 @@
       </c>
       <c r="S234" t="inlineStr">
         <is>
-          <t>17-01-2021 08:30</t>
+          <t>2021-01-17 08:30:00</t>
         </is>
       </c>
       <c r="T234" t="inlineStr"/>
@@ -22853,7 +22853,7 @@
       </c>
       <c r="S235" t="inlineStr">
         <is>
-          <t>17-02-2021 08:30</t>
+          <t>2021-02-17 08:30:00</t>
         </is>
       </c>
       <c r="T235" t="inlineStr"/>
@@ -22946,7 +22946,7 @@
       </c>
       <c r="S236" t="inlineStr">
         <is>
-          <t>01-03-2021 08:30</t>
+          <t>2021-01-03 08:30:00</t>
         </is>
       </c>
       <c r="T236" t="inlineStr"/>
@@ -23039,7 +23039,7 @@
       </c>
       <c r="S237" t="inlineStr">
         <is>
-          <t>07-01-2021 08:30</t>
+          <t>2021-07-01 08:30:00</t>
         </is>
       </c>
       <c r="T237" t="inlineStr"/>
@@ -23132,7 +23132,7 @@
       </c>
       <c r="S238" t="inlineStr">
         <is>
-          <t>10-02-2021 08:30</t>
+          <t>2021-10-02 08:30:00</t>
         </is>
       </c>
       <c r="T238" t="inlineStr"/>
@@ -23225,7 +23225,7 @@
       </c>
       <c r="S239" t="inlineStr">
         <is>
-          <t>10-03-2021 08:30</t>
+          <t>2021-10-03 08:30:00</t>
         </is>
       </c>
       <c r="T239" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="S240" t="inlineStr">
         <is>
-          <t>12-01-2021 08:30</t>
+          <t>2021-12-01 08:30:00</t>
         </is>
       </c>
       <c r="T240" t="inlineStr"/>
@@ -23411,7 +23411,7 @@
       </c>
       <c r="S241" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T241" t="inlineStr"/>
@@ -23504,7 +23504,7 @@
       </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>13-01-2021 08:30</t>
+          <t>2021-01-13 08:30:00</t>
         </is>
       </c>
       <c r="T242" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="S243" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T243" t="n">
@@ -23706,7 +23706,7 @@
       </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>12-10-2021 08:30</t>
+          <t>2021-12-10 08:30:00</t>
         </is>
       </c>
       <c r="T244" t="n">
@@ -23807,7 +23807,7 @@
       </c>
       <c r="S245" t="inlineStr">
         <is>
-          <t>11-01-2021 08:30</t>
+          <t>2021-11-01 08:30:00</t>
         </is>
       </c>
       <c r="T245" t="inlineStr"/>
@@ -23900,7 +23900,7 @@
       </c>
       <c r="S246" t="inlineStr">
         <is>
-          <t>08-02-2021 08:30</t>
+          <t>2021-08-02 08:30:00</t>
         </is>
       </c>
       <c r="T246" t="inlineStr"/>
@@ -23993,7 +23993,7 @@
       </c>
       <c r="S247" t="inlineStr">
         <is>
-          <t>08-03-2021 08:30</t>
+          <t>2021-08-03 08:30:00</t>
         </is>
       </c>
       <c r="T247" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="S248" t="inlineStr">
         <is>
-          <t>13-04-2021 08:30</t>
+          <t>2021-04-13 08:30:00</t>
         </is>
       </c>
       <c r="T248" t="n">
@@ -24187,7 +24187,7 @@
       </c>
       <c r="S249" t="inlineStr">
         <is>
-          <t>30-10-2021 08:30</t>
+          <t>2021-10-30 08:30:00</t>
         </is>
       </c>
       <c r="T249" t="n">
